--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7582,6 +7582,434 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>121897110</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78616</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Portfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>436815</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7161466</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Ulf Arup, Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>121897104</v>
+      </c>
+      <c r="B62" t="n">
+        <v>77956</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Portfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>436661</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7162094</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Ulf Arup, Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121897105</v>
+      </c>
+      <c r="B63" t="n">
+        <v>74727</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Portfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>436661</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7162094</v>
+      </c>
+      <c r="S63" t="n">
+        <v>20</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Ulf Arup, Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>121897106</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78779</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Portfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>436661</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7162094</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ola Hammarström, Ulf Arup, Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -7691,10 +7691,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121897104</v>
+        <v>121897106</v>
       </c>
       <c r="B62" t="n">
-        <v>77956</v>
+        <v>78779</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7703,25 +7703,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6443</v>
+        <v>1249</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121897106</v>
+        <v>121897104</v>
       </c>
       <c r="B64" t="n">
-        <v>78779</v>
+        <v>77956</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7917,25 +7917,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1249</v>
+        <v>6443</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -7584,10 +7584,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121897110</v>
+        <v>121897105</v>
       </c>
       <c r="B61" t="n">
-        <v>78616</v>
+        <v>74727</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7600,21 +7600,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7624,10 +7624,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>436815</v>
+        <v>436661</v>
       </c>
       <c r="R61" t="n">
-        <v>7161466</v>
+        <v>7162094</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7798,10 +7798,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121897105</v>
+        <v>121897110</v>
       </c>
       <c r="B63" t="n">
-        <v>74727</v>
+        <v>78616</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436661</v>
+        <v>436815</v>
       </c>
       <c r="R63" t="n">
-        <v>7162094</v>
+        <v>7161466</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -7584,10 +7584,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121897105</v>
+        <v>121897104</v>
       </c>
       <c r="B61" t="n">
-        <v>74727</v>
+        <v>77956</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7596,25 +7596,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1467</v>
+        <v>6443</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121897104</v>
+        <v>121897105</v>
       </c>
       <c r="B64" t="n">
-        <v>77956</v>
+        <v>74727</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7917,25 +7917,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6443</v>
+        <v>1467</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -7584,10 +7584,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121897104</v>
+        <v>121897105</v>
       </c>
       <c r="B61" t="n">
-        <v>77956</v>
+        <v>74740</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7596,25 +7596,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6443</v>
+        <v>1467</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121897106</v>
+        <v>121897104</v>
       </c>
       <c r="B62" t="n">
-        <v>78779</v>
+        <v>77969</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7703,25 +7703,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1249</v>
+        <v>6443</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7801,7 +7801,7 @@
         <v>121897110</v>
       </c>
       <c r="B63" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121897105</v>
+        <v>121897106</v>
       </c>
       <c r="B64" t="n">
-        <v>74727</v>
+        <v>78792</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7917,25 +7917,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -7587,7 +7587,7 @@
         <v>121897105</v>
       </c>
       <c r="B61" t="n">
-        <v>74740</v>
+        <v>74742</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121897104</v>
+        <v>121897106</v>
       </c>
       <c r="B62" t="n">
-        <v>77969</v>
+        <v>78794</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7703,25 +7703,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6443</v>
+        <v>1249</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7801,7 +7801,7 @@
         <v>121897110</v>
       </c>
       <c r="B63" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121897106</v>
+        <v>121897104</v>
       </c>
       <c r="B64" t="n">
-        <v>78792</v>
+        <v>77971</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7917,25 +7917,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1249</v>
+        <v>6443</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -7691,10 +7691,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121897106</v>
+        <v>121897104</v>
       </c>
       <c r="B62" t="n">
-        <v>78794</v>
+        <v>77972</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7703,25 +7703,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1249</v>
+        <v>6443</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7801,7 +7801,7 @@
         <v>121897110</v>
       </c>
       <c r="B63" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121897104</v>
+        <v>121897106</v>
       </c>
       <c r="B64" t="n">
-        <v>77971</v>
+        <v>78795</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7917,25 +7917,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6443</v>
+        <v>1249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -7584,10 +7584,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121897105</v>
+        <v>121897106</v>
       </c>
       <c r="B61" t="n">
-        <v>74742</v>
+        <v>78802</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7596,25 +7596,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7694,7 +7694,7 @@
         <v>121897104</v>
       </c>
       <c r="B62" t="n">
-        <v>77972</v>
+        <v>77979</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>121897110</v>
       </c>
       <c r="B63" t="n">
-        <v>78632</v>
+        <v>78639</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121897106</v>
+        <v>121897105</v>
       </c>
       <c r="B64" t="n">
-        <v>78795</v>
+        <v>74746</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7917,25 +7917,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1249</v>
+        <v>1467</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -7584,10 +7584,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121897104</v>
+        <v>121897105</v>
       </c>
       <c r="B61" t="n">
-        <v>77985</v>
+        <v>74752</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7596,25 +7596,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6443</v>
+        <v>1467</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121897105</v>
+        <v>121897104</v>
       </c>
       <c r="B62" t="n">
-        <v>74752</v>
+        <v>77985</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7703,25 +7703,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1467</v>
+        <v>6443</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7798,10 +7798,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121897110</v>
+        <v>121897106</v>
       </c>
       <c r="B63" t="n">
-        <v>78645</v>
+        <v>78808</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7810,25 +7810,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7838,10 +7838,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436815</v>
+        <v>436661</v>
       </c>
       <c r="R63" t="n">
-        <v>7161466</v>
+        <v>7162094</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121897106</v>
+        <v>121897110</v>
       </c>
       <c r="B64" t="n">
-        <v>78808</v>
+        <v>78645</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7917,25 +7917,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7945,10 +7945,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436661</v>
+        <v>436815</v>
       </c>
       <c r="R64" t="n">
-        <v>7162094</v>
+        <v>7161466</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -7584,10 +7584,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121897105</v>
+        <v>121897106</v>
       </c>
       <c r="B61" t="n">
-        <v>74752</v>
+        <v>78809</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7596,25 +7596,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1467</v>
+        <v>1249</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121897104</v>
+        <v>121897110</v>
       </c>
       <c r="B62" t="n">
-        <v>77985</v>
+        <v>78646</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7703,25 +7703,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6443</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>436661</v>
+        <v>436815</v>
       </c>
       <c r="R62" t="n">
-        <v>7162094</v>
+        <v>7161466</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7798,10 +7798,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121897106</v>
+        <v>121897104</v>
       </c>
       <c r="B63" t="n">
-        <v>78808</v>
+        <v>77986</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7810,25 +7810,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1249</v>
+        <v>6443</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121897110</v>
+        <v>121897105</v>
       </c>
       <c r="B64" t="n">
-        <v>78645</v>
+        <v>74752</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7921,21 +7921,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7945,10 +7945,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>436815</v>
+        <v>436661</v>
       </c>
       <c r="R64" t="n">
-        <v>7161466</v>
+        <v>7162094</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8010,6 +8010,117 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125556315</v>
+      </c>
+      <c r="B65" t="n">
+        <v>75020</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>310</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Chaenotheca laevigata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Finnkruhögarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>436787</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7161507</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Ulf Arup, Ola Hammarström, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -8015,7 +8015,7 @@
         <v>125556315</v>
       </c>
       <c r="B65" t="n">
-        <v>75061</v>
+        <v>75062</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -8015,7 +8015,7 @@
         <v>125556315</v>
       </c>
       <c r="B65" t="n">
-        <v>75062</v>
+        <v>75063</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Måns Svensson, Ulf Arup, Ola Hammarström, Martin Westberg</t>
+          <t>Martin Westberg, Ola Hammarström, Ulf Arup, Måns Svensson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 68481-2020 artfynd.xlsx
+++ b/artfynd/A 68481-2020 artfynd.xlsx
@@ -8111,7 +8111,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ola Hammarström, Ulf Arup, Måns Svensson</t>
+          <t>Måns Svensson, Ulf Arup, Ola Hammarström, Martin Westberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
